--- a/src/ParaBankAutomation/Data/RegistrationData.xlsx
+++ b/src/ParaBankAutomation/Data/RegistrationData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\7-GitHub\ParaBankAutomation\src\ParaBankAutomation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCEEBCDA-5076-4CAD-9C7D-B5390D1D4AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D5662A-EDCB-4854-98BD-56214FB6889F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4425" yWindow="2985" windowWidth="21600" windowHeight="11295" xr2:uid="{1F374D62-BD17-437E-A352-C9AD64027BFF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>First Name</t>
   </si>
@@ -77,78 +77,12 @@
     <t>Ademir</t>
   </si>
   <si>
-    <t>Samira</t>
-  </si>
-  <si>
-    <t>Marcela</t>
-  </si>
-  <si>
-    <t>Oton</t>
-  </si>
-  <si>
-    <t>Barbara</t>
-  </si>
-  <si>
-    <t>Cecília</t>
-  </si>
-  <si>
-    <t>Marcos</t>
-  </si>
-  <si>
-    <t>Roberto</t>
-  </si>
-  <si>
-    <t>Mario</t>
-  </si>
-  <si>
-    <t>Emerson</t>
-  </si>
-  <si>
-    <t>Camila</t>
-  </si>
-  <si>
-    <t>Sabrina</t>
-  </si>
-  <si>
     <t>Couves</t>
   </si>
   <si>
     <t>Silva</t>
   </si>
   <si>
-    <t>Augusta</t>
-  </si>
-  <si>
-    <t>Santos</t>
-  </si>
-  <si>
-    <t>Oliveira</t>
-  </si>
-  <si>
-    <t>Maria</t>
-  </si>
-  <si>
-    <t>Ramos</t>
-  </si>
-  <si>
-    <t>Sampaio</t>
-  </si>
-  <si>
-    <t>Carlos</t>
-  </si>
-  <si>
-    <t>Sergio</t>
-  </si>
-  <si>
-    <t>Fitpaldi</t>
-  </si>
-  <si>
-    <t>Sonza</t>
-  </si>
-  <si>
-    <t>Sato</t>
-  </si>
-  <si>
     <t>Rio de Janeiro</t>
   </si>
   <si>
@@ -161,88 +95,16 @@
     <t>Rua 03</t>
   </si>
   <si>
-    <t>Rua 04</t>
-  </si>
-  <si>
-    <t>Rua 05</t>
-  </si>
-  <si>
-    <t>Rua 06</t>
-  </si>
-  <si>
-    <t>Rua 07</t>
-  </si>
-  <si>
-    <t>Rua 08</t>
-  </si>
-  <si>
-    <t>Rua 09</t>
-  </si>
-  <si>
-    <t>Rua 10</t>
-  </si>
-  <si>
-    <t>Rua 11</t>
-  </si>
-  <si>
-    <t>Rua 12</t>
-  </si>
-  <si>
-    <t>Rua 13</t>
-  </si>
-  <si>
-    <t>Rua 14</t>
-  </si>
-  <si>
     <t>RJ</t>
   </si>
   <si>
     <t>AC</t>
   </si>
   <si>
-    <t>Porto Velho</t>
-  </si>
-  <si>
-    <t>RO</t>
-  </si>
-  <si>
     <t>ZeCouves</t>
   </si>
   <si>
     <t>AdemirSilva</t>
-  </si>
-  <si>
-    <t>SamiraAugusta</t>
-  </si>
-  <si>
-    <t>MarcelaSantos</t>
-  </si>
-  <si>
-    <t>OtonOliveira</t>
-  </si>
-  <si>
-    <t>BarbaraMaria</t>
-  </si>
-  <si>
-    <t>CecíliaRamos</t>
-  </si>
-  <si>
-    <t>MarcosSampaio</t>
-  </si>
-  <si>
-    <t>RobertoCarlos</t>
-  </si>
-  <si>
-    <t>MarioSergio</t>
-  </si>
-  <si>
-    <t>EmersonFitpaldi</t>
-  </si>
-  <si>
-    <t>CamilaSonza</t>
-  </si>
-  <si>
-    <t>SabrinaSato</t>
   </si>
 </sst>
 </file>
@@ -636,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D140953-ED94-48AC-B349-51181B1D5979}">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -692,16 +554,16 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="G2">
         <v>10020030</v>
@@ -713,7 +575,7 @@
         <v>1234567891</v>
       </c>
       <c r="J2" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="K2">
         <v>123456</v>
@@ -727,16 +589,16 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="G3">
         <v>10020031</v>
@@ -748,397 +610,14 @@
         <v>1234567892</v>
       </c>
       <c r="J3" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="K3">
         <v>123456</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4">
-        <v>10020032</v>
-      </c>
-      <c r="H4">
-        <v>123456783</v>
-      </c>
-      <c r="I4">
-        <v>1234567893</v>
-      </c>
-      <c r="J4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K4">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5">
-        <v>10020033</v>
-      </c>
-      <c r="H5">
-        <v>123456784</v>
-      </c>
-      <c r="I5">
-        <v>1234567894</v>
-      </c>
-      <c r="J5" t="s">
-        <v>59</v>
-      </c>
-      <c r="K5">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6">
-        <v>10020034</v>
-      </c>
-      <c r="H6">
-        <v>123456785</v>
-      </c>
-      <c r="I6">
-        <v>1234567895</v>
-      </c>
-      <c r="J6" t="s">
-        <v>60</v>
-      </c>
-      <c r="K6">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7">
-        <v>10020035</v>
-      </c>
-      <c r="H7">
-        <v>123456786</v>
-      </c>
-      <c r="I7">
-        <v>1234567896</v>
-      </c>
-      <c r="J7" t="s">
-        <v>61</v>
-      </c>
-      <c r="K7">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8">
-        <v>10020036</v>
-      </c>
-      <c r="H8">
-        <v>123456787</v>
-      </c>
-      <c r="I8">
-        <v>1234567897</v>
-      </c>
-      <c r="J8" t="s">
-        <v>62</v>
-      </c>
-      <c r="K8">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9">
-        <v>10020037</v>
-      </c>
-      <c r="H9">
-        <v>123456788</v>
-      </c>
-      <c r="I9">
-        <v>1234567898</v>
-      </c>
-      <c r="J9" t="s">
-        <v>63</v>
-      </c>
-      <c r="K9">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10">
-        <v>10020038</v>
-      </c>
-      <c r="H10">
-        <v>123456789</v>
-      </c>
-      <c r="I10">
-        <v>1234567899</v>
-      </c>
-      <c r="J10" t="s">
-        <v>64</v>
-      </c>
-      <c r="K10">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11">
-        <v>10020039</v>
-      </c>
-      <c r="H11">
-        <v>123456790</v>
-      </c>
-      <c r="I11">
-        <v>1234567900</v>
-      </c>
-      <c r="J11" t="s">
-        <v>65</v>
-      </c>
-      <c r="K11">
-        <v>123456</v>
-      </c>
-    </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12">
-        <v>10020040</v>
-      </c>
-      <c r="H12">
-        <v>123456791</v>
-      </c>
-      <c r="I12">
-        <v>1234567901</v>
-      </c>
-      <c r="J12" t="s">
-        <v>66</v>
-      </c>
-      <c r="K12">
-        <v>123456</v>
-      </c>
       <c r="N12" s="2"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" t="s">
-        <v>54</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13">
-        <v>10020041</v>
-      </c>
-      <c r="H13">
-        <v>123456792</v>
-      </c>
-      <c r="I13">
-        <v>1234567902</v>
-      </c>
-      <c r="J13" t="s">
-        <v>67</v>
-      </c>
-      <c r="K13">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14">
-        <v>10020042</v>
-      </c>
-      <c r="H14">
-        <v>123456793</v>
-      </c>
-      <c r="I14">
-        <v>1234567903</v>
-      </c>
-      <c r="J14" t="s">
-        <v>68</v>
-      </c>
-      <c r="K14">
-        <v>123456</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
